--- a/data/availability/projects/palm-hills-developments/village-de-la-capitale.xlsx
+++ b/data/availability/projects/palm-hills-developments/village-de-la-capitale.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for village-de-la-capitale</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -909,7 +919,6 @@
       <c r="G2" t="n">
         <v>146</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -966,7 +975,6 @@
       <c r="G3" t="n">
         <v>146</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1023,7 +1031,6 @@
       <c r="G4" t="n">
         <v>146</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1080,7 +1087,6 @@
       <c r="G5" t="n">
         <v>61.5</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1137,7 +1143,6 @@
       <c r="G6" t="n">
         <v>94</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1194,7 +1199,6 @@
       <c r="G7" t="n">
         <v>62.5</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1251,7 +1255,6 @@
       <c r="G8" t="n">
         <v>146</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1308,7 +1311,6 @@
       <c r="G9" t="n">
         <v>61.5</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1365,7 +1367,6 @@
       <c r="G10" t="n">
         <v>94</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1422,7 +1423,6 @@
       <c r="G11" t="n">
         <v>146</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1479,7 +1479,6 @@
       <c r="G12" t="n">
         <v>62.5</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1536,7 +1535,6 @@
       <c r="G13" t="n">
         <v>146</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1593,7 +1591,6 @@
       <c r="G14" t="n">
         <v>61.5</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1650,7 +1647,6 @@
       <c r="G15" t="n">
         <v>94</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1707,7 +1703,6 @@
       <c r="G16" t="n">
         <v>146</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1764,7 +1759,6 @@
       <c r="G17" t="n">
         <v>61.5</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1821,7 +1815,6 @@
       <c r="G18" t="n">
         <v>94</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1878,7 +1871,6 @@
       <c r="G19" t="n">
         <v>146</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1935,7 +1927,6 @@
       <c r="G20" t="n">
         <v>146</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1992,7 +1983,6 @@
       <c r="G21" t="n">
         <v>61.5</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2049,7 +2039,6 @@
       <c r="G22" t="n">
         <v>94</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2106,7 +2095,6 @@
       <c r="G23" t="n">
         <v>146</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2163,7 +2151,6 @@
       <c r="G24" t="n">
         <v>61.5</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2220,7 +2207,6 @@
       <c r="G25" t="n">
         <v>94</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2277,7 +2263,6 @@
       <c r="G26" t="n">
         <v>146</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2334,7 +2319,6 @@
       <c r="G27" t="n">
         <v>146</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2391,7 +2375,6 @@
       <c r="G28" t="n">
         <v>61.5</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2448,7 +2431,6 @@
       <c r="G29" t="n">
         <v>94</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2505,7 +2487,6 @@
       <c r="G30" t="n">
         <v>146</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2562,7 +2543,6 @@
       <c r="G31" t="n">
         <v>146</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2619,7 +2599,6 @@
       <c r="G32" t="n">
         <v>61.5</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2676,7 +2655,6 @@
       <c r="G33" t="n">
         <v>146</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2733,7 +2711,6 @@
       <c r="G34" t="n">
         <v>94</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2790,7 +2767,6 @@
       <c r="G35" t="n">
         <v>62.5</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2847,7 +2823,6 @@
       <c r="G36" t="n">
         <v>262</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2904,7 +2879,6 @@
       <c r="G37" t="n">
         <v>262</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2961,7 +2935,6 @@
       <c r="G38" t="n">
         <v>262</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3018,7 +2991,6 @@
       <c r="G39" t="n">
         <v>262</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3075,7 +3047,6 @@
       <c r="G40" t="n">
         <v>262</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3132,7 +3103,6 @@
       <c r="G41" t="n">
         <v>262</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3189,7 +3159,6 @@
       <c r="G42" t="n">
         <v>262</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3246,7 +3215,6 @@
       <c r="G43" t="n">
         <v>262</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3303,7 +3271,6 @@
       <c r="G44" t="n">
         <v>262</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3360,7 +3327,6 @@
       <c r="G45" t="n">
         <v>185</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3417,7 +3383,6 @@
       <c r="G46" t="n">
         <v>185</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3474,7 +3439,6 @@
       <c r="G47" t="n">
         <v>185</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3531,7 +3495,6 @@
       <c r="G48" t="n">
         <v>185</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3588,7 +3551,6 @@
       <c r="G49" t="n">
         <v>185</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3645,7 +3607,6 @@
       <c r="G50" t="n">
         <v>185</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3702,7 +3663,6 @@
       <c r="G51" t="n">
         <v>185</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3759,7 +3719,6 @@
       <c r="G52" t="n">
         <v>185</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3816,7 +3775,6 @@
       <c r="G53" t="n">
         <v>185</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3873,7 +3831,6 @@
       <c r="G54" t="n">
         <v>185</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3930,7 +3887,6 @@
       <c r="G55" t="n">
         <v>185</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3987,7 +3943,6 @@
       <c r="G56" t="n">
         <v>185</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4044,7 +3999,6 @@
       <c r="G57" t="n">
         <v>185</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4101,7 +4055,6 @@
       <c r="G58" t="n">
         <v>185</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4158,7 +4111,6 @@
       <c r="G59" t="n">
         <v>185</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4215,7 +4167,6 @@
       <c r="G60" t="n">
         <v>176.5</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4272,7 +4223,6 @@
       <c r="G61" t="n">
         <v>176.5</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4329,7 +4279,6 @@
       <c r="G62" t="n">
         <v>176.5</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4386,7 +4335,6 @@
       <c r="G63" t="n">
         <v>176.5</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4443,7 +4391,6 @@
       <c r="G64" t="n">
         <v>146.5</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4500,7 +4447,6 @@
       <c r="G65" t="n">
         <v>146.5</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4557,7 +4503,6 @@
       <c r="G66" t="n">
         <v>146.5</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4614,7 +4559,6 @@
       <c r="G67" t="n">
         <v>146.5</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4671,7 +4615,6 @@
       <c r="G68" t="n">
         <v>146.5</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4728,7 +4671,6 @@
       <c r="G69" t="n">
         <v>146.5</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4785,7 +4727,6 @@
       <c r="G70" t="n">
         <v>146.5</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4842,7 +4783,6 @@
       <c r="G71" t="n">
         <v>146.5</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4899,7 +4839,6 @@
       <c r="G72" t="n">
         <v>146.5</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4956,7 +4895,6 @@
       <c r="G73" t="n">
         <v>146.5</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5013,7 +4951,6 @@
       <c r="G74" t="n">
         <v>146.5</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5070,7 +5007,6 @@
       <c r="G75" t="n">
         <v>146.5</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5127,7 +5063,6 @@
       <c r="G76" t="n">
         <v>146.5</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5184,7 +5119,6 @@
       <c r="G77" t="n">
         <v>146.5</v>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5241,7 +5175,6 @@
       <c r="G78" t="n">
         <v>146.5</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5298,7 +5231,6 @@
       <c r="G79" t="n">
         <v>146.5</v>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5355,7 +5287,6 @@
       <c r="G80" t="n">
         <v>146.5</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5412,7 +5343,6 @@
       <c r="G81" t="n">
         <v>146.5</v>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5469,7 +5399,6 @@
       <c r="G82" t="n">
         <v>146.5</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5526,7 +5455,6 @@
       <c r="G83" t="n">
         <v>146.5</v>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5583,7 +5511,6 @@
       <c r="G84" t="n">
         <v>146.5</v>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5640,7 +5567,6 @@
       <c r="G85" t="n">
         <v>146.5</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5697,7 +5623,6 @@
       <c r="G86" t="n">
         <v>146.5</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5754,7 +5679,6 @@
       <c r="G87" t="n">
         <v>146.5</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5811,7 +5735,6 @@
       <c r="G88" t="n">
         <v>146.5</v>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5868,7 +5791,6 @@
       <c r="G89" t="n">
         <v>146.5</v>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5925,7 +5847,6 @@
       <c r="G90" t="n">
         <v>146.5</v>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5982,7 +5903,6 @@
       <c r="G91" t="n">
         <v>146.5</v>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6039,7 +5959,6 @@
       <c r="G92" t="n">
         <v>146.5</v>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6096,7 +6015,6 @@
       <c r="G93" t="n">
         <v>146.5</v>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6153,7 +6071,6 @@
       <c r="G94" t="n">
         <v>146.5</v>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6210,7 +6127,6 @@
       <c r="G95" t="n">
         <v>146.5</v>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6267,7 +6183,6 @@
       <c r="G96" t="n">
         <v>146.5</v>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6324,7 +6239,6 @@
       <c r="G97" t="n">
         <v>146.5</v>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6381,7 +6295,6 @@
       <c r="G98" t="n">
         <v>146.5</v>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6438,7 +6351,6 @@
       <c r="G99" t="n">
         <v>146.5</v>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6495,7 +6407,6 @@
       <c r="G100" t="n">
         <v>146.5</v>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6552,7 +6463,6 @@
       <c r="G101" t="n">
         <v>146.5</v>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6609,7 +6519,6 @@
       <c r="G102" t="n">
         <v>146.5</v>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6666,7 +6575,6 @@
       <c r="G103" t="n">
         <v>146.5</v>
       </c>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6723,7 +6631,6 @@
       <c r="G104" t="n">
         <v>146.5</v>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6780,7 +6687,6 @@
       <c r="G105" t="n">
         <v>146.5</v>
       </c>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6837,7 +6743,6 @@
       <c r="G106" t="n">
         <v>146.5</v>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6894,7 +6799,6 @@
       <c r="G107" t="n">
         <v>146.5</v>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6951,7 +6855,6 @@
       <c r="G108" t="n">
         <v>146.5</v>
       </c>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7008,7 +6911,6 @@
       <c r="G109" t="n">
         <v>146.5</v>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7065,7 +6967,6 @@
       <c r="G110" t="n">
         <v>146.5</v>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7122,7 +7023,6 @@
       <c r="G111" t="n">
         <v>146.5</v>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7179,7 +7079,6 @@
       <c r="G112" t="n">
         <v>146.5</v>
       </c>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7236,7 +7135,6 @@
       <c r="G113" t="n">
         <v>146.5</v>
       </c>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7293,7 +7191,6 @@
       <c r="G114" t="n">
         <v>146.5</v>
       </c>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7350,7 +7247,6 @@
       <c r="G115" t="n">
         <v>146.5</v>
       </c>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7407,7 +7303,6 @@
       <c r="G116" t="n">
         <v>146.5</v>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7464,7 +7359,6 @@
       <c r="G117" t="n">
         <v>146.5</v>
       </c>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7521,7 +7415,6 @@
       <c r="G118" t="n">
         <v>146.5</v>
       </c>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7578,7 +7471,6 @@
       <c r="G119" t="n">
         <v>146.5</v>
       </c>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7635,7 +7527,6 @@
       <c r="G120" t="n">
         <v>146.5</v>
       </c>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7692,7 +7583,6 @@
       <c r="G121" t="n">
         <v>146.5</v>
       </c>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7749,7 +7639,6 @@
       <c r="G122" t="n">
         <v>146.5</v>
       </c>
-      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7806,7 +7695,6 @@
       <c r="G123" t="n">
         <v>146.5</v>
       </c>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7863,7 +7751,6 @@
       <c r="G124" t="n">
         <v>146.5</v>
       </c>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7920,7 +7807,6 @@
       <c r="G125" t="n">
         <v>146.5</v>
       </c>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7977,7 +7863,6 @@
       <c r="G126" t="n">
         <v>146.5</v>
       </c>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8034,7 +7919,6 @@
       <c r="G127" t="n">
         <v>146.5</v>
       </c>
-      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8091,7 +7975,6 @@
       <c r="G128" t="n">
         <v>146.5</v>
       </c>
-      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8148,7 +8031,6 @@
       <c r="G129" t="n">
         <v>146.5</v>
       </c>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8205,7 +8087,6 @@
       <c r="G130" t="n">
         <v>146.5</v>
       </c>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8262,7 +8143,6 @@
       <c r="G131" t="n">
         <v>146.5</v>
       </c>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8319,7 +8199,6 @@
       <c r="G132" t="n">
         <v>146.5</v>
       </c>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8376,7 +8255,6 @@
       <c r="G133" t="n">
         <v>146.5</v>
       </c>
-      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8433,7 +8311,6 @@
       <c r="G134" t="n">
         <v>146.5</v>
       </c>
-      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8490,7 +8367,6 @@
       <c r="G135" t="n">
         <v>146.5</v>
       </c>
-      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8547,7 +8423,6 @@
       <c r="G136" t="n">
         <v>146.5</v>
       </c>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8604,7 +8479,6 @@
       <c r="G137" t="n">
         <v>146.5</v>
       </c>
-      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8661,7 +8535,6 @@
       <c r="G138" t="n">
         <v>146.5</v>
       </c>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8718,7 +8591,6 @@
       <c r="G139" t="n">
         <v>146.5</v>
       </c>
-      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8775,7 +8647,6 @@
       <c r="G140" t="n">
         <v>146.5</v>
       </c>
-      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8832,7 +8703,6 @@
       <c r="G141" t="n">
         <v>146.5</v>
       </c>
-      <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8889,7 +8759,6 @@
       <c r="G142" t="n">
         <v>146.5</v>
       </c>
-      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8946,7 +8815,6 @@
       <c r="G143" t="n">
         <v>146.5</v>
       </c>
-      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9003,7 +8871,6 @@
       <c r="G144" t="n">
         <v>146.5</v>
       </c>
-      <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9060,7 +8927,6 @@
       <c r="G145" t="n">
         <v>146.5</v>
       </c>
-      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9117,7 +8983,6 @@
       <c r="G146" t="n">
         <v>146.5</v>
       </c>
-      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9174,7 +9039,6 @@
       <c r="G147" t="n">
         <v>146.5</v>
       </c>
-      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9231,7 +9095,6 @@
       <c r="G148" t="n">
         <v>146.5</v>
       </c>
-      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9288,7 +9151,6 @@
       <c r="G149" t="n">
         <v>146.5</v>
       </c>
-      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9345,7 +9207,6 @@
       <c r="G150" t="n">
         <v>146.5</v>
       </c>
-      <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9402,7 +9263,6 @@
       <c r="G151" t="n">
         <v>146.5</v>
       </c>
-      <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9459,7 +9319,6 @@
       <c r="G152" t="n">
         <v>146.5</v>
       </c>
-      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9516,7 +9375,6 @@
       <c r="G153" t="n">
         <v>146.5</v>
       </c>
-      <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9573,7 +9431,6 @@
       <c r="G154" t="n">
         <v>146.5</v>
       </c>
-      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9630,7 +9487,6 @@
       <c r="G155" t="n">
         <v>146.5</v>
       </c>
-      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9687,7 +9543,6 @@
       <c r="G156" t="n">
         <v>146.5</v>
       </c>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9744,7 +9599,6 @@
       <c r="G157" t="n">
         <v>146.5</v>
       </c>
-      <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9801,7 +9655,6 @@
       <c r="G158" t="n">
         <v>146.5</v>
       </c>
-      <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9858,7 +9711,6 @@
       <c r="G159" t="n">
         <v>146.5</v>
       </c>
-      <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9915,7 +9767,6 @@
       <c r="G160" t="n">
         <v>146.5</v>
       </c>
-      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9972,7 +9823,6 @@
       <c r="G161" t="n">
         <v>146.5</v>
       </c>
-      <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10029,7 +9879,6 @@
       <c r="G162" t="n">
         <v>146.5</v>
       </c>
-      <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10086,7 +9935,6 @@
       <c r="G163" t="n">
         <v>146.5</v>
       </c>
-      <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10143,7 +9991,6 @@
       <c r="G164" t="n">
         <v>146.5</v>
       </c>
-      <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10200,7 +10047,6 @@
       <c r="G165" t="n">
         <v>146.5</v>
       </c>
-      <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10257,7 +10103,6 @@
       <c r="G166" t="n">
         <v>146.5</v>
       </c>
-      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10314,7 +10159,6 @@
       <c r="G167" t="n">
         <v>146.5</v>
       </c>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10371,7 +10215,6 @@
       <c r="G168" t="n">
         <v>146.5</v>
       </c>
-      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10428,7 +10271,6 @@
       <c r="G169" t="n">
         <v>146.5</v>
       </c>
-      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10485,7 +10327,6 @@
       <c r="G170" t="n">
         <v>146.5</v>
       </c>
-      <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10542,7 +10383,6 @@
       <c r="G171" t="n">
         <v>146.5</v>
       </c>
-      <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10599,7 +10439,6 @@
       <c r="G172" t="n">
         <v>146.5</v>
       </c>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10656,7 +10495,6 @@
       <c r="G173" t="n">
         <v>146.5</v>
       </c>
-      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10713,7 +10551,6 @@
       <c r="G174" t="n">
         <v>146.5</v>
       </c>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10770,7 +10607,6 @@
       <c r="G175" t="n">
         <v>146.5</v>
       </c>
-      <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10827,7 +10663,6 @@
       <c r="G176" t="n">
         <v>146.5</v>
       </c>
-      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10884,7 +10719,6 @@
       <c r="G177" t="n">
         <v>146.5</v>
       </c>
-      <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10941,7 +10775,6 @@
       <c r="G178" t="n">
         <v>146.5</v>
       </c>
-      <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10998,7 +10831,6 @@
       <c r="G179" t="n">
         <v>146.5</v>
       </c>
-      <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11055,7 +10887,6 @@
       <c r="G180" t="n">
         <v>146.5</v>
       </c>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11112,7 +10943,6 @@
       <c r="G181" t="n">
         <v>146.5</v>
       </c>
-      <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11169,7 +10999,6 @@
       <c r="G182" t="n">
         <v>146.5</v>
       </c>
-      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11226,7 +11055,6 @@
       <c r="G183" t="n">
         <v>146.5</v>
       </c>
-      <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11283,7 +11111,6 @@
       <c r="G184" t="n">
         <v>146.5</v>
       </c>
-      <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11340,7 +11167,6 @@
       <c r="G185" t="n">
         <v>146</v>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11397,7 +11223,6 @@
       <c r="G186" t="n">
         <v>146</v>
       </c>
-      <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11454,7 +11279,6 @@
       <c r="G187" t="n">
         <v>146</v>
       </c>
-      <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11511,7 +11335,6 @@
       <c r="G188" t="n">
         <v>94</v>
       </c>
-      <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11568,7 +11391,6 @@
       <c r="G189" t="n">
         <v>146</v>
       </c>
-      <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11625,7 +11447,6 @@
       <c r="G190" t="n">
         <v>146</v>
       </c>
-      <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11682,7 +11503,6 @@
       <c r="G191" t="n">
         <v>146</v>
       </c>
-      <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11739,7 +11559,6 @@
       <c r="G192" t="n">
         <v>146</v>
       </c>
-      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11796,7 +11615,6 @@
       <c r="G193" t="n">
         <v>146</v>
       </c>
-      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11853,7 +11671,6 @@
       <c r="G194" t="n">
         <v>146</v>
       </c>
-      <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11910,7 +11727,6 @@
       <c r="G195" t="n">
         <v>146</v>
       </c>
-      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11967,7 +11783,6 @@
       <c r="G196" t="n">
         <v>146</v>
       </c>
-      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12024,7 +11839,6 @@
       <c r="G197" t="n">
         <v>146</v>
       </c>
-      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12081,7 +11895,6 @@
       <c r="G198" t="n">
         <v>146</v>
       </c>
-      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12138,7 +11951,6 @@
       <c r="G199" t="n">
         <v>146</v>
       </c>
-      <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12195,7 +12007,6 @@
       <c r="G200" t="n">
         <v>146</v>
       </c>
-      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12252,7 +12063,6 @@
       <c r="G201" t="n">
         <v>146</v>
       </c>
-      <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12309,7 +12119,6 @@
       <c r="G202" t="n">
         <v>146</v>
       </c>
-      <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12366,7 +12175,6 @@
       <c r="G203" t="n">
         <v>146</v>
       </c>
-      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12423,7 +12231,6 @@
       <c r="G204" t="n">
         <v>146</v>
       </c>
-      <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12480,7 +12287,6 @@
       <c r="G205" t="n">
         <v>146</v>
       </c>
-      <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12537,7 +12343,6 @@
       <c r="G206" t="n">
         <v>146</v>
       </c>
-      <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12594,7 +12399,6 @@
       <c r="G207" t="n">
         <v>146</v>
       </c>
-      <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12651,7 +12455,6 @@
       <c r="G208" t="n">
         <v>146</v>
       </c>
-      <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12708,7 +12511,6 @@
       <c r="G209" t="n">
         <v>146</v>
       </c>
-      <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12765,7 +12567,6 @@
       <c r="G210" t="n">
         <v>146</v>
       </c>
-      <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12822,7 +12623,6 @@
       <c r="G211" t="n">
         <v>185</v>
       </c>
-      <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12879,7 +12679,6 @@
       <c r="G212" t="n">
         <v>185</v>
       </c>
-      <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12936,7 +12735,6 @@
       <c r="G213" t="n">
         <v>185</v>
       </c>
-      <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12993,7 +12791,6 @@
       <c r="G214" t="n">
         <v>185</v>
       </c>
-      <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13050,7 +12847,6 @@
       <c r="G215" t="n">
         <v>185</v>
       </c>
-      <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13107,7 +12903,6 @@
       <c r="G216" t="n">
         <v>185</v>
       </c>
-      <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13164,7 +12959,6 @@
       <c r="G217" t="n">
         <v>185</v>
       </c>
-      <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13221,7 +13015,6 @@
       <c r="G218" t="n">
         <v>185</v>
       </c>
-      <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13278,7 +13071,6 @@
       <c r="G219" t="n">
         <v>185</v>
       </c>
-      <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13335,7 +13127,6 @@
       <c r="G220" t="n">
         <v>185</v>
       </c>
-      <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13392,7 +13183,6 @@
       <c r="G221" t="n">
         <v>185</v>
       </c>
-      <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13449,7 +13239,6 @@
       <c r="G222" t="n">
         <v>185</v>
       </c>
-      <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13506,7 +13295,6 @@
       <c r="G223" t="n">
         <v>185</v>
       </c>
-      <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13563,7 +13351,6 @@
       <c r="G224" t="n">
         <v>185</v>
       </c>
-      <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13620,7 +13407,6 @@
       <c r="G225" t="n">
         <v>185</v>
       </c>
-      <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13677,7 +13463,6 @@
       <c r="G226" t="n">
         <v>185</v>
       </c>
-      <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13734,7 +13519,6 @@
       <c r="G227" t="n">
         <v>185</v>
       </c>
-      <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13791,7 +13575,6 @@
       <c r="G228" t="n">
         <v>185</v>
       </c>
-      <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13848,7 +13631,6 @@
       <c r="G229" t="n">
         <v>185</v>
       </c>
-      <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13905,7 +13687,6 @@
       <c r="G230" t="n">
         <v>176.5</v>
       </c>
-      <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13962,7 +13743,6 @@
       <c r="G231" t="n">
         <v>176.5</v>
       </c>
-      <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14019,7 +13799,6 @@
       <c r="G232" t="n">
         <v>176.5</v>
       </c>
-      <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14076,7 +13855,6 @@
       <c r="G233" t="n">
         <v>96</v>
       </c>
-      <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14133,7 +13911,6 @@
       <c r="G234" t="n">
         <v>102</v>
       </c>
-      <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14190,7 +13967,6 @@
       <c r="G235" t="n">
         <v>150</v>
       </c>
-      <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14247,7 +14023,6 @@
       <c r="G236" t="n">
         <v>96</v>
       </c>
-      <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14304,7 +14079,6 @@
       <c r="G237" t="n">
         <v>96.5</v>
       </c>
-      <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14361,7 +14135,6 @@
       <c r="G238" t="n">
         <v>102</v>
       </c>
-      <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14418,7 +14191,6 @@
       <c r="G239" t="n">
         <v>150</v>
       </c>
-      <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14475,7 +14247,6 @@
       <c r="G240" t="n">
         <v>96</v>
       </c>
-      <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14532,7 +14303,6 @@
       <c r="G241" t="n">
         <v>96.5</v>
       </c>
-      <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14589,7 +14359,6 @@
       <c r="G242" t="n">
         <v>102</v>
       </c>
-      <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14646,7 +14415,6 @@
       <c r="G243" t="n">
         <v>150</v>
       </c>
-      <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14703,7 +14471,6 @@
       <c r="G244" t="n">
         <v>96</v>
       </c>
-      <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14760,7 +14527,6 @@
       <c r="G245" t="n">
         <v>96.5</v>
       </c>
-      <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14817,7 +14583,6 @@
       <c r="G246" t="n">
         <v>102</v>
       </c>
-      <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14874,7 +14639,6 @@
       <c r="G247" t="n">
         <v>150</v>
       </c>
-      <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14931,7 +14695,6 @@
       <c r="G248" t="n">
         <v>96</v>
       </c>
-      <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14988,7 +14751,6 @@
       <c r="G249" t="n">
         <v>96.5</v>
       </c>
-      <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15045,7 +14807,6 @@
       <c r="G250" t="n">
         <v>102</v>
       </c>
-      <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15102,7 +14863,6 @@
       <c r="G251" t="n">
         <v>150</v>
       </c>
-      <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15159,7 +14919,6 @@
       <c r="G252" t="n">
         <v>96</v>
       </c>
-      <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15216,7 +14975,6 @@
       <c r="G253" t="n">
         <v>96.5</v>
       </c>
-      <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15273,7 +15031,6 @@
       <c r="G254" t="n">
         <v>102</v>
       </c>
-      <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15330,7 +15087,6 @@
       <c r="G255" t="n">
         <v>150</v>
       </c>
-      <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15387,7 +15143,6 @@
       <c r="G256" t="n">
         <v>96</v>
       </c>
-      <c r="H256" t="inlineStr"/>
       <c r="I256" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15444,7 +15199,6 @@
       <c r="G257" t="n">
         <v>96.5</v>
       </c>
-      <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15501,7 +15255,6 @@
       <c r="G258" t="n">
         <v>102</v>
       </c>
-      <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15558,7 +15311,6 @@
       <c r="G259" t="n">
         <v>150</v>
       </c>
-      <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15615,7 +15367,6 @@
       <c r="G260" t="n">
         <v>96</v>
       </c>
-      <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15672,7 +15423,6 @@
       <c r="G261" t="n">
         <v>96.5</v>
       </c>
-      <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15729,7 +15479,6 @@
       <c r="G262" t="n">
         <v>102</v>
       </c>
-      <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15786,7 +15535,6 @@
       <c r="G263" t="n">
         <v>150</v>
       </c>
-      <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15843,7 +15591,6 @@
       <c r="G264" t="n">
         <v>150</v>
       </c>
-      <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15900,7 +15647,6 @@
       <c r="G265" t="n">
         <v>150</v>
       </c>
-      <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr">
         <is>
           <t>Landscape</t>

--- a/data/availability/projects/palm-hills-developments/village-de-la-capitale.xlsx
+++ b/data/availability/projects/palm-hills-developments/village-de-la-capitale.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -664,7 +664,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -895,7 +895,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6999,7 +6999,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7279,7 +7279,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9575,7 +9575,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10135,7 +10135,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10303,7 +10303,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10527,7 +10527,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11367,7 +11367,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11423,7 +11423,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11703,7 +11703,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12095,7 +12095,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12263,7 +12263,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12319,7 +12319,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -12487,7 +12487,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -12543,7 +12543,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13831,7 +13831,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -13887,7 +13887,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -13943,7 +13943,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -13999,7 +13999,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14055,7 +14055,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14167,7 +14167,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -14223,7 +14223,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -14279,7 +14279,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -14447,7 +14447,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -14503,7 +14503,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -14559,7 +14559,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -14615,7 +14615,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -14671,7 +14671,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -14783,7 +14783,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -14895,7 +14895,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15007,7 +15007,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15063,7 +15063,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -15231,7 +15231,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -15287,7 +15287,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -15343,7 +15343,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -15399,7 +15399,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -15511,7 +15511,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -15567,7 +15567,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -15623,7 +15623,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">

--- a/data/availability/projects/palm-hills-developments/village-de-la-capitale.xlsx
+++ b/data/availability/projects/palm-hills-developments/village-de-la-capitale.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -597,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -647,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -697,7 +697,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -747,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -797,7 +797,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -6999,7 +6999,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7279,7 +7279,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8377,7 +8377,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9273,7 +9273,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -9575,7 +9575,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10057,7 +10057,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -10135,7 +10135,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10225,7 +10225,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -10303,7 +10303,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10505,7 +10505,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -10527,7 +10527,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10673,7 +10673,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10729,7 +10729,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11009,7 +11009,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -11367,7 +11367,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -11423,7 +11423,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11457,7 +11457,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -11703,7 +11703,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11737,7 +11737,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -12095,7 +12095,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -12263,7 +12263,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -12319,7 +12319,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -12487,7 +12487,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -12543,7 +12543,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -12689,7 +12689,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -12745,7 +12745,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -12913,7 +12913,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13025,7 +13025,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13081,7 +13081,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -13103,7 +13103,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13137,7 +13137,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -13159,7 +13159,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -13249,7 +13249,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -13327,7 +13327,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -13383,7 +13383,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -13439,7 +13439,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -13473,7 +13473,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -13529,7 +13529,7 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -13585,7 +13585,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -13697,7 +13697,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -13719,7 +13719,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -13809,7 +13809,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -13831,7 +13831,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -13865,7 +13865,7 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -13887,7 +13887,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -13921,7 +13921,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -13943,7 +13943,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -13977,7 +13977,7 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -13999,7 +13999,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14033,7 +14033,7 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -14055,7 +14055,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14145,7 +14145,7 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -14167,7 +14167,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -14201,7 +14201,7 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -14223,7 +14223,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -14257,7 +14257,7 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -14279,7 +14279,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -14369,7 +14369,7 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -14425,7 +14425,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -14447,7 +14447,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -14481,7 +14481,7 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -14503,7 +14503,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -14559,7 +14559,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -14593,7 +14593,7 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -14615,7 +14615,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -14671,7 +14671,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -14761,7 +14761,7 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -14783,7 +14783,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -14817,7 +14817,7 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -14873,7 +14873,7 @@
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -14895,7 +14895,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -14929,7 +14929,7 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -14985,7 +14985,7 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -15007,7 +15007,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -15063,7 +15063,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -15097,7 +15097,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -15153,7 +15153,7 @@
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -15209,7 +15209,7 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -15231,7 +15231,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -15265,7 +15265,7 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -15287,7 +15287,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -15321,7 +15321,7 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -15343,7 +15343,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -15399,7 +15399,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -15511,7 +15511,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -15545,7 +15545,7 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -15567,7 +15567,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -15601,7 +15601,7 @@
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -15623,7 +15623,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -15657,7 +15657,7 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">

--- a/data/availability/projects/palm-hills-developments/village-de-la-capitale.xlsx
+++ b/data/availability/projects/palm-hills-developments/village-de-la-capitale.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -647,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -697,7 +697,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8377,7 +8377,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -9273,7 +9273,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10057,7 +10057,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -10225,7 +10225,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -10505,7 +10505,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -10673,7 +10673,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -10729,7 +10729,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -11009,7 +11009,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -11457,7 +11457,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -11737,7 +11737,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -12689,7 +12689,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -12745,7 +12745,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -12913,7 +12913,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -13025,7 +13025,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -13081,7 +13081,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -13137,7 +13137,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -13249,7 +13249,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -13473,7 +13473,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -13529,7 +13529,7 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -13585,7 +13585,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -13697,7 +13697,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -13753,7 +13753,7 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -13809,7 +13809,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -13831,7 +13831,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -13865,7 +13865,7 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -13887,7 +13887,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -13921,7 +13921,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -13977,7 +13977,7 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -13999,7 +13999,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14033,7 +14033,7 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -14055,7 +14055,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14145,7 +14145,7 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -14201,7 +14201,7 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -14223,7 +14223,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -14257,7 +14257,7 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -14279,7 +14279,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -14369,7 +14369,7 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -14425,7 +14425,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -14447,7 +14447,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -14481,7 +14481,7 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -14503,7 +14503,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -14559,7 +14559,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -14593,7 +14593,7 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -14671,7 +14671,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -14761,7 +14761,7 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -14783,7 +14783,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -14817,7 +14817,7 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -14873,7 +14873,7 @@
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -14895,7 +14895,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -14929,7 +14929,7 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -14985,7 +14985,7 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -15007,7 +15007,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -15097,7 +15097,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -15153,7 +15153,7 @@
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -15209,7 +15209,7 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -15231,7 +15231,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -15265,7 +15265,7 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -15321,7 +15321,7 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -15343,7 +15343,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -15399,7 +15399,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -15545,7 +15545,7 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -15601,7 +15601,7 @@
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -15657,7 +15657,7 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>2030 (4 Years)</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
